--- a/public/downloads/Confronto_Ammortamento_Acquisto_vs_Leasing.xlsx
+++ b/public/downloads/Confronto_Ammortamento_Acquisto_vs_Leasing.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisto vs Leasing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confronto Ammortamento" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00 &quot;€&quot;"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0 &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="0 &quot;anni&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00 &quot;€&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,7 +45,19 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00293C5B"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00293C5B"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FE6F3A"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -53,8 +67,8 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00293C5B"/>
-      <sz val="12"/>
+      <color rgb="00664CCD"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -66,21 +80,21 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0016A34A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00664CCD"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7ED"/>
+        <bgColor rgb="00FFF7ED"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -94,8 +108,14 @@
         <bgColor rgb="00F8F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,47 +123,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00FE6F3A"/>
+      </left>
+      <right style="medium">
+        <color rgb="00FE6F3A"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FE6F3A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FE6F3A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -508,682 +562,1221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00664CCD"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Confronto ammortamento: Acquisto diretto vs Leasing finanziario</t>
+          <t>Confronto ammortamento: Ordinario vs Iperammortamento vs Leasing</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Art. 102, c. 7 TUIR (L. 147/2013) — Durata minima leasing = 1/2 vita utile fiscale</t>
+          <t>Modifica le celle arancioni per aggiornare automaticamente tutti i calcoli</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Costo impianto FV</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>130.000 €</t>
+          <t>PARAMETRI (modifica qui)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Coefficiente ammortamento (DM 1988)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Costo impianto (€, netto IVA)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>130000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Vita utile fiscale (acquisto)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>11 anni</t>
-        </is>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Coefficiente ammortamento DM 1988</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Durata deduzione leasing (metà)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>6 anni</t>
-        </is>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Maggiorazione iperammortamento</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Aliquota IRES + IRAP</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>27,8%</t>
-        </is>
+      <c r="B8" s="6" t="n">
+        <v>0.278</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Iperammortamento maggiorazione</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>+180%</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Durata leasing (anni)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>VALORI CALCOLATI</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>SCENARIO A — Acquisto diretto</t>
-        </is>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Vita utile fiscale (anni)</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <f>ROUND(1/B6,0)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Costo ammortizzabile iper (280%)</t>
+        </is>
+      </c>
+      <c r="B13" s="11">
+        <f>B5*(1+B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Maggiorazione netta (€)</t>
+        </is>
+      </c>
+      <c r="B14" s="11">
+        <f>B5*B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Quota ammortamento ordinario annua</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>B5*B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Quota ammortamento iper annua (su 280%)</t>
+        </is>
+      </c>
+      <c r="B16" s="11">
+        <f>B13*B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Deduzione leasing annua (quota capitale)</t>
+        </is>
+      </c>
+      <c r="B17" s="11">
+        <f>B5/B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Deduzione leasing iper annua (280%/durata)</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
+        <f>B13/B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>SCENARIO A — Acquisto diretto (ammortamento ordinario + iperammortamento)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Anno</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Amm. ordinario</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Amm. iper (+180%)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Totale deducibile</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Risparmio fiscale</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Cumulato</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Residuo da ammortizzare</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>9107.280000000001</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="B22" s="14">
+        <f>IF(A22&lt;=B12, MIN(B15, B5), 0)</f>
+        <v/>
+      </c>
+      <c r="C22" s="14">
+        <f>IF(A22&lt;=B12, MIN(B16-B15, B14), 0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="14">
+        <f>B22+C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="14">
+        <f>D22*B8</f>
+        <v/>
+      </c>
+      <c r="F22" s="14">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="14">
+        <f>B13-SUM(D22:D22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>18214.56</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="B23" s="16">
+        <f>IF(A23&lt;=B12, MIN(B15, B5-SUM(B22:B22)), 0)</f>
+        <v/>
+      </c>
+      <c r="C23" s="16">
+        <f>IF(A23&lt;=B12, MIN(B16-B15, B14-SUM(C22:C22)), 0)</f>
+        <v/>
+      </c>
+      <c r="D23" s="16">
+        <f>B23+C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="16">
+        <f>D23*B8</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
+        <f>F22+E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="16">
+        <f>B13-SUM(D22:D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>27321.84</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="B24" s="14">
+        <f>IF(A24&lt;=B12, MIN(B15, B5-SUM(B22:B23)), 0)</f>
+        <v/>
+      </c>
+      <c r="C24" s="14">
+        <f>IF(A24&lt;=B12, MIN(B16-B15, B14-SUM(C22:C23)), 0)</f>
+        <v/>
+      </c>
+      <c r="D24" s="14">
+        <f>B24+C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="14">
+        <f>D24*B8</f>
+        <v/>
+      </c>
+      <c r="F24" s="14">
+        <f>F23+E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="14">
+        <f>B13-SUM(D22:D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>36429.12</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="B25" s="16">
+        <f>IF(A25&lt;=B12, MIN(B15, B5-SUM(B22:B24)), 0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="16">
+        <f>IF(A25&lt;=B12, MIN(B16-B15, B14-SUM(C22:C24)), 0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>B25+C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="16">
+        <f>D25*B8</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
+        <f>F24+E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="16">
+        <f>B13-SUM(D22:D25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B18" s="8" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>45536.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="B26" s="14">
+        <f>IF(A26&lt;=B12, MIN(B15, B5-SUM(B22:B25)), 0)</f>
+        <v/>
+      </c>
+      <c r="C26" s="14">
+        <f>IF(A26&lt;=B12, MIN(B16-B15, B14-SUM(C22:C25)), 0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="14">
+        <f>B26+C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="14">
+        <f>D26*B8</f>
+        <v/>
+      </c>
+      <c r="F26" s="14">
+        <f>F25+E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="14">
+        <f>B13-SUM(D22:D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="10" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>54643.68</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="B27" s="16">
+        <f>IF(A27&lt;=B12, MIN(B15, B5-SUM(B22:B26)), 0)</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>IF(A27&lt;=B12, MIN(B16-B15, B14-SUM(C22:C26)), 0)</f>
+        <v/>
+      </c>
+      <c r="D27" s="16">
+        <f>B27+C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="16">
+        <f>D27*B8</f>
+        <v/>
+      </c>
+      <c r="F27" s="16">
+        <f>F26+E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="16">
+        <f>B13-SUM(D22:D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="8" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>63750.96</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="B28" s="14">
+        <f>IF(A28&lt;=B12, MIN(B15, B5-SUM(B22:B27)), 0)</f>
+        <v/>
+      </c>
+      <c r="C28" s="14">
+        <f>IF(A28&lt;=B12, MIN(B16-B15, B14-SUM(C22:C27)), 0)</f>
+        <v/>
+      </c>
+      <c r="D28" s="14">
+        <f>B28+C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="14">
+        <f>D28*B8</f>
+        <v/>
+      </c>
+      <c r="F28" s="14">
+        <f>F27+E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
+        <f>B13-SUM(D22:D28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>72858.24000000001</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="B29" s="16">
+        <f>IF(A29&lt;=B12, MIN(B15, B5-SUM(B22:B28)), 0)</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f>IF(A29&lt;=B12, MIN(B16-B15, B14-SUM(C22:C28)), 0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="16">
+        <f>B29+C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="16">
+        <f>D29*B8</f>
+        <v/>
+      </c>
+      <c r="F29" s="16">
+        <f>F28+E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="16">
+        <f>B13-SUM(D22:D29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>81965.52</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="n">
+      <c r="B30" s="14">
+        <f>IF(A30&lt;=B12, MIN(B15, B5-SUM(B22:B29)), 0)</f>
+        <v/>
+      </c>
+      <c r="C30" s="14">
+        <f>IF(A30&lt;=B12, MIN(B16-B15, B14-SUM(C22:C29)), 0)</f>
+        <v/>
+      </c>
+      <c r="D30" s="14">
+        <f>B30+C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="14">
+        <f>D30*B8</f>
+        <v/>
+      </c>
+      <c r="F30" s="14">
+        <f>F29+E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="14">
+        <f>B13-SUM(D22:D30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>91072.8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="B31" s="16">
+        <f>IF(A31&lt;=B12, MIN(B15, B5-SUM(B22:B30)), 0)</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>IF(A31&lt;=B12, MIN(B16-B15, B14-SUM(C22:C30)), 0)</f>
+        <v/>
+      </c>
+      <c r="D31" s="16">
+        <f>B31+C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f>D31*B8</f>
+        <v/>
+      </c>
+      <c r="F31" s="16">
+        <f>F30+E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="16">
+        <f>B13-SUM(D22:D31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B24" s="8" t="n">
-        <v>11700</v>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>21060</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>32760</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>100180.08</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>SCENARIO B — Leasing finanziario (ammortamento dimezzato)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="B32" s="14">
+        <f>IF(A32&lt;=B12, MIN(B15, B5-SUM(B22:B31)), 0)</f>
+        <v/>
+      </c>
+      <c r="C32" s="14">
+        <f>IF(A32&lt;=B12, MIN(B16-B15, B14-SUM(C22:C31)), 0)</f>
+        <v/>
+      </c>
+      <c r="D32" s="14">
+        <f>B32+C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="14">
+        <f>D32*B8</f>
+        <v/>
+      </c>
+      <c r="F32" s="14">
+        <f>F31+E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="14">
+        <f>B13-SUM(D22:D32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" s="16">
+        <f>IF(A33&lt;=B12, MIN(B15, B5-SUM(B22:B32)), 0)</f>
+        <v/>
+      </c>
+      <c r="C33" s="16">
+        <f>IF(A33&lt;=B12, MIN(B16-B15, B14-SUM(C22:C32)), 0)</f>
+        <v/>
+      </c>
+      <c r="D33" s="16">
+        <f>B33+C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="16">
+        <f>D33*B8</f>
+        <v/>
+      </c>
+      <c r="F33" s="16">
+        <f>F32+E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="16">
+        <f>B13-SUM(D22:D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B34" s="14">
+        <f>IF(A34&lt;=B12, MIN(B15, B5-SUM(B22:B33)), 0)</f>
+        <v/>
+      </c>
+      <c r="C34" s="14">
+        <f>IF(A34&lt;=B12, MIN(B16-B15, B14-SUM(C22:C33)), 0)</f>
+        <v/>
+      </c>
+      <c r="D34" s="14">
+        <f>B34+C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="14">
+        <f>D34*B8</f>
+        <v/>
+      </c>
+      <c r="F34" s="14">
+        <f>F33+E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="14">
+        <f>B13-SUM(D22:D34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B35" s="16">
+        <f>IF(A35&lt;=B12, MIN(B15, B5-SUM(B22:B34)), 0)</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>IF(A35&lt;=B12, MIN(B16-B15, B14-SUM(C22:C34)), 0)</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>B35+C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f>D35*B8</f>
+        <v/>
+      </c>
+      <c r="F35" s="16">
+        <f>F34+E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="16">
+        <f>B13-SUM(D22:D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" s="14">
+        <f>IF(A36&lt;=B12, MIN(B15, B5-SUM(B22:B35)), 0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="14">
+        <f>IF(A36&lt;=B12, MIN(B16-B15, B14-SUM(C22:C35)), 0)</f>
+        <v/>
+      </c>
+      <c r="D36" s="14">
+        <f>B36+C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="14">
+        <f>D36*B8</f>
+        <v/>
+      </c>
+      <c r="F36" s="14">
+        <f>F35+E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="14">
+        <f>B13-SUM(D22:D36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>TOTALE</t>
+        </is>
+      </c>
+      <c r="B38" s="18">
+        <f>SUM(B22:B36)</f>
+        <v/>
+      </c>
+      <c r="C38" s="18">
+        <f>SUM(C22:C36)</f>
+        <v/>
+      </c>
+      <c r="D38" s="18">
+        <f>SUM(D22:D36)</f>
+        <v/>
+      </c>
+      <c r="E38" s="18">
+        <f>SUM(E22:E36)</f>
+        <v/>
+      </c>
+      <c r="F38" s="19">
+        <f>F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>SCENARIO B — Leasing finanziario (ammortamento dimezzato, Art. 102 c.7 TUIR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Anno</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>Deduz. canoni (q.ta capitale)</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Deduz. iper (+180%)</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Deduz. iper (280%/durata)</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>Totale deducibile</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Risparmio fiscale</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>Cumulato</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Residuo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="8" t="n">
-        <v>21666.67</v>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>39000</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>60666.67</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>16865.33</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>16865.33</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="B42" s="14">
+        <f>IF(A42&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C42" s="14">
+        <f>IF(A42&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="14">
+        <f>B42+C42</f>
+        <v/>
+      </c>
+      <c r="E42" s="14">
+        <f>D42*B8</f>
+        <v/>
+      </c>
+      <c r="F42" s="14">
+        <f>E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="14">
+        <f>B13-SUM(D42:D42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="10" t="n">
-        <v>21666.67</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>39000</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>60666.67</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>16865.33</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>33730.67</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="B43" s="16">
+        <f>IF(A43&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C43" s="16">
+        <f>IF(A43&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D43" s="16">
+        <f>B43+C43</f>
+        <v/>
+      </c>
+      <c r="E43" s="16">
+        <f>D43*B8</f>
+        <v/>
+      </c>
+      <c r="F43" s="16">
+        <f>F42+E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="16">
+        <f>B13-SUM(D42:D43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="8" t="n">
-        <v>21666.67</v>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>39000</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>60666.67</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>16865.33</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>50596</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="B44" s="14">
+        <f>IF(A44&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C44" s="14">
+        <f>IF(A44&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D44" s="14">
+        <f>B44+C44</f>
+        <v/>
+      </c>
+      <c r="E44" s="14">
+        <f>D44*B8</f>
+        <v/>
+      </c>
+      <c r="F44" s="14">
+        <f>F43+E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="14">
+        <f>B13-SUM(D42:D44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="10" t="n">
-        <v>21666.67</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>39000</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>60666.67</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>16865.33</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>67461.33</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="B45" s="16">
+        <f>IF(A45&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C45" s="16">
+        <f>IF(A45&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D45" s="16">
+        <f>B45+C45</f>
+        <v/>
+      </c>
+      <c r="E45" s="16">
+        <f>D45*B8</f>
+        <v/>
+      </c>
+      <c r="F45" s="16">
+        <f>F44+E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="16">
+        <f>B13-SUM(D42:D45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B32" s="8" t="n">
-        <v>21666.67</v>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>39000</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>60666.67</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>16865.33</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>84326.67</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="n">
+      <c r="B46" s="14">
+        <f>IF(A46&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C46" s="14">
+        <f>IF(A46&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D46" s="14">
+        <f>B46+C46</f>
+        <v/>
+      </c>
+      <c r="E46" s="14">
+        <f>D46*B8</f>
+        <v/>
+      </c>
+      <c r="F46" s="14">
+        <f>F45+E46</f>
+        <v/>
+      </c>
+      <c r="G46" s="14">
+        <f>B13-SUM(D42:D46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="10" t="n">
-        <v>21666.67</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>39000</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>60666.67</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>16865.33</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>101192</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>RIEPILOGO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr"/>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B47" s="16">
+        <f>IF(A47&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C47" s="16">
+        <f>IF(A47&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D47" s="16">
+        <f>B47+C47</f>
+        <v/>
+      </c>
+      <c r="E47" s="16">
+        <f>D47*B8</f>
+        <v/>
+      </c>
+      <c r="F47" s="16">
+        <f>F46+E47</f>
+        <v/>
+      </c>
+      <c r="G47" s="16">
+        <f>B13-SUM(D42:D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" s="14">
+        <f>IF(A48&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C48" s="14">
+        <f>IF(A48&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D48" s="14">
+        <f>B48+C48</f>
+        <v/>
+      </c>
+      <c r="E48" s="14">
+        <f>D48*B8</f>
+        <v/>
+      </c>
+      <c r="F48" s="14">
+        <f>F47+E48</f>
+        <v/>
+      </c>
+      <c r="G48" s="14">
+        <f>B13-SUM(D42:D48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" s="16">
+        <f>IF(A49&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C49" s="16">
+        <f>IF(A49&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D49" s="16">
+        <f>B49+C49</f>
+        <v/>
+      </c>
+      <c r="E49" s="16">
+        <f>D49*B8</f>
+        <v/>
+      </c>
+      <c r="F49" s="16">
+        <f>F48+E49</f>
+        <v/>
+      </c>
+      <c r="G49" s="16">
+        <f>B13-SUM(D42:D49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B50" s="14">
+        <f>IF(A50&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C50" s="14">
+        <f>IF(A50&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D50" s="14">
+        <f>B50+C50</f>
+        <v/>
+      </c>
+      <c r="E50" s="14">
+        <f>D50*B8</f>
+        <v/>
+      </c>
+      <c r="F50" s="14">
+        <f>F49+E50</f>
+        <v/>
+      </c>
+      <c r="G50" s="14">
+        <f>B13-SUM(D42:D50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B51" s="16">
+        <f>IF(A51&lt;=B9, B17, 0)</f>
+        <v/>
+      </c>
+      <c r="C51" s="16">
+        <f>IF(A51&lt;=B9, B14/B9, 0)</f>
+        <v/>
+      </c>
+      <c r="D51" s="16">
+        <f>B51+C51</f>
+        <v/>
+      </c>
+      <c r="E51" s="16">
+        <f>D51*B8</f>
+        <v/>
+      </c>
+      <c r="F51" s="16">
+        <f>F50+E51</f>
+        <v/>
+      </c>
+      <c r="G51" s="16">
+        <f>B13-SUM(D42:D51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>TOTALE</t>
+        </is>
+      </c>
+      <c r="B52" s="18">
+        <f>SUM(B42:B51)</f>
+        <v/>
+      </c>
+      <c r="C52" s="18">
+        <f>SUM(C42:C51)</f>
+        <v/>
+      </c>
+      <c r="D52" s="18">
+        <f>SUM(D42:D51)</f>
+        <v/>
+      </c>
+      <c r="E52" s="18">
+        <f>SUM(E42:E51)</f>
+        <v/>
+      </c>
+      <c r="F52" s="19">
+        <f>F51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RIEPILOGO COMPARATIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr"/>
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>Acquisto diretto</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>Leasing finanziario</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Vantaggio leasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Periodo di deduzione</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>11 anni</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>6 anni</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>-5 anni</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="B56" s="20">
+        <f>B12&amp;" anni"</f>
+        <v/>
+      </c>
+      <c r="C56" s="20">
+        <f>B9&amp;" anni"</f>
+        <v/>
+      </c>
+      <c r="D56" s="21">
+        <f>(B12-B9)&amp;" anni in meno"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>Beneficio fiscale totale</t>
+        </is>
+      </c>
+      <c r="B57" s="16">
+        <f>F36</f>
+        <v/>
+      </c>
+      <c r="C57" s="16">
+        <f>F51</f>
+        <v/>
+      </c>
+      <c r="D57" s="23">
+        <f>C57-B57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Risparmio fiscale anno 1</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n">
-        <v>9107.280000000001</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>16865.33</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>7758.05</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="B58" s="14">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="C58" s="14">
+        <f>E42</f>
+        <v/>
+      </c>
+      <c r="D58" s="23">
+        <f>C58-B58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>Risparmio cumulato anno 3</t>
+        </is>
+      </c>
+      <c r="B59" s="16">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="C59" s="16">
+        <f>F44</f>
+        <v/>
+      </c>
+      <c r="D59" s="23">
+        <f>C59-B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Risparmio cumulato anno 5</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n">
-        <v>45536.4</v>
-      </c>
-      <c r="C39" s="8" t="n">
-        <v>84326.67</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>38790.27</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>Beneficio totale</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>100180.08</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>101192</v>
-      </c>
-      <c r="D40" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="B60" s="14">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="C60" s="14">
+        <f>F46</f>
+        <v/>
+      </c>
+      <c r="D60" s="23">
+        <f>C60-B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Note:</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>• Art. 102, comma 7, TUIR — mod. L. 147/2013 (Stabilità 2014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>• Durata minima leasing beni mobili = 1/2 periodo ammortamento (dal 01/01/2014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>• Beni immobili: durata minima fissa 12 anni (non si applica la regola della metà)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>• L'iperammortamento 2026 (L. 199/2025) si deduce nella stessa durata del leasing</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>• Aliquota: 27,8% (IRES 24% + IRAP 3,8%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>• Le celle arancioni sono modificabili: cambia il costo impianto e tutti i calcoli si aggiornano</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>• Art. 102, comma 7, TUIR (mod. L. 147/2013): durata minima leasing beni mobili = 1/2 vita utile</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>• Iperammortamento 2026 (L. 199/2025): costo ammortizzabile al 280% (100% ordinario + 180% maggiorazione)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>• Aliquota 27,8% = IRES 24% + IRAP 3,8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>• Impianto FV classificato bene mobile (coeff. 9%, DM 31/12/1988)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>• Il beneficio totale è identico, ma il leasing anticipa il cash-flow fiscale</t>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>• Il beneficio fiscale totale è identico, ma il leasing anticipa il cash-flow nei primi anni</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A26:F26"/>
+  <mergeCells count="6">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
